--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC VIII/LTAIPT_A63F08B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC VIII/LTAIPT_A63F08B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -100,28 +100,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t/>
+    <t>2023</t>
   </si>
   <si>
     <t>Departamento de Recursos Humanos</t>
   </si>
   <si>
-    <t>El tabulador de sueldos 2022 se encuentra en proceso de aurización, mediante Oficio D.AD.300/2022 en Oficialia Mayor de Gobierno.</t>
-  </si>
-  <si>
-    <t>C2372AFE8974075041DB666C97D5CEEB</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>14/10/2022</t>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto%20Recursos%20Humanos/2do%20Trimestre/Tabulador%202023.%20Of.D.AD.0357-2023.pdf</t>
+  </si>
+  <si>
+    <t>C0AD0062953BEF8D370ED30D49873E8F</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>13/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de julio de 2023 al 30 de septiembre del 2023, El tabulador de sueldos 2023 de este Colegio de Bachilleres del Estado de Tlaxcala,se encuentra en proceso de autorización, mediante Oficio DIR.AD.0357/2023 ante Oficialia Mayor de Gobierno del Estado de Tlaxcala.</t>
   </si>
 </sst>
 </file>
@@ -517,15 +517,15 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="137.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="145.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="112.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="244.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -658,31 +658,31 @@
     </row>
     <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
